--- a/artfynd/A 53419-2020 artfynd.xlsx
+++ b/artfynd/A 53419-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 53419-2020 artfynd.xlsx
+++ b/artfynd/A 53419-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -928,6 +928,131 @@
       <c r="AY3" t="inlineStr">
         <is>
           <t>Norrbottens flora 2010</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>123477581</v>
+      </c>
+      <c r="B4" t="n">
+        <v>98818</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>222685</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Flotagräs</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Sparganium gramineum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Georgi</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Slumptjärnens sydväststrand, Nb</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>851719</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7336741</v>
+      </c>
+      <c r="S4" t="n">
+        <v>100</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Kalix</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Töre</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>BD-Kal-0278</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2008-09-04</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2008-09-04</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Slumptjärnens sydväststrand, Obskoord: 7334755/1815455/100 m (). Norrbottens flora - 2010.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>mager tjärn</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>jan Ahlm</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 53419-2020 artfynd.xlsx
+++ b/artfynd/A 53419-2020 artfynd.xlsx
@@ -936,7 +936,7 @@
         <v>123477581</v>
       </c>
       <c r="B4" t="n">
-        <v>98818</v>
+        <v>98824</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 53419-2020 artfynd.xlsx
+++ b/artfynd/A 53419-2020 artfynd.xlsx
@@ -936,7 +936,7 @@
         <v>123477581</v>
       </c>
       <c r="B4" t="n">
-        <v>98824</v>
+        <v>98827</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 53419-2020 artfynd.xlsx
+++ b/artfynd/A 53419-2020 artfynd.xlsx
@@ -936,7 +936,7 @@
         <v>123477581</v>
       </c>
       <c r="B4" t="n">
-        <v>98827</v>
+        <v>98844</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 53419-2020 artfynd.xlsx
+++ b/artfynd/A 53419-2020 artfynd.xlsx
@@ -936,7 +936,7 @@
         <v>123477581</v>
       </c>
       <c r="B4" t="n">
-        <v>98844</v>
+        <v>98941</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 53419-2020 artfynd.xlsx
+++ b/artfynd/A 53419-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -928,131 +928,6 @@
       <c r="AY3" t="inlineStr">
         <is>
           <t>Norrbottens flora 2010</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>123477581</v>
-      </c>
-      <c r="B4" t="n">
-        <v>98941</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>222685</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Flotagräs</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Sparganium gramineum</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Georgi</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Slumptjärnens sydväststrand, Nb</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>851719</v>
-      </c>
-      <c r="R4" t="n">
-        <v>7336741</v>
-      </c>
-      <c r="S4" t="n">
-        <v>100</v>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Kalix</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Töre</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>BD-Kal-0278</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2008-09-04</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>2008-09-04</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Slumptjärnens sydväststrand, Obskoord: 7334755/1815455/100 m (). Norrbottens flora - 2010.</t>
-        </is>
-      </c>
-      <c r="AD4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF4" t="inlineStr"/>
-      <c r="AG4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>mager tjärn</t>
-        </is>
-      </c>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>Jan Yngve Andersson</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>jan Ahlm</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
         </is>
       </c>
     </row>
